--- a/hpi_scraper/JobsHiring/apollo/raw_exports/info_and_diagnostics/apollo_field_provenance.xlsx
+++ b/hpi_scraper/JobsHiring/apollo/raw_exports/info_and_diagnostics/apollo_field_provenance.xlsx
@@ -445,7 +445,7 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
@@ -500,12 +500,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
